--- a/artfynd/A 20665-2025 artfynd.xlsx
+++ b/artfynd/A 20665-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125772365</v>
       </c>
       <c r="B2" t="n">
-        <v>105908</v>
+        <v>105915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20665-2025 artfynd.xlsx
+++ b/artfynd/A 20665-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125772365</v>
       </c>
       <c r="B2" t="n">
-        <v>105915</v>
+        <v>105918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20665-2025 artfynd.xlsx
+++ b/artfynd/A 20665-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125772365</v>
       </c>
       <c r="B2" t="n">
-        <v>105918</v>
+        <v>105922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20665-2025 artfynd.xlsx
+++ b/artfynd/A 20665-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125772365</v>
       </c>
       <c r="B2" t="n">
-        <v>105922</v>
+        <v>105923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20665-2025 artfynd.xlsx
+++ b/artfynd/A 20665-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125772365</v>
       </c>
       <c r="B2" t="n">
-        <v>105923</v>
+        <v>105925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20665-2025 artfynd.xlsx
+++ b/artfynd/A 20665-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125772365</v>
       </c>
       <c r="B2" t="n">
-        <v>105925</v>
+        <v>105927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20665-2025 artfynd.xlsx
+++ b/artfynd/A 20665-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125772365</v>
       </c>
       <c r="B2" t="n">
-        <v>105927</v>
+        <v>105931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20665-2025 artfynd.xlsx
+++ b/artfynd/A 20665-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125772365</v>
       </c>
       <c r="B2" t="n">
-        <v>105931</v>
+        <v>105944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20665-2025 artfynd.xlsx
+++ b/artfynd/A 20665-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125772365</v>
       </c>
       <c r="B2" t="n">
-        <v>105944</v>
+        <v>105947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
